--- a/ETF.xlsx
+++ b/ETF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88063529-4238-4D55-9046-ABA0D185B182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2110CD71-1E1F-4EAA-A443-274577416446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,21 +68,12 @@
     <t>IG</t>
   </si>
   <si>
-    <t>https://www.blackrock.com/es/profesionales/productos/331714</t>
-  </si>
-  <si>
     <t>ID29</t>
   </si>
   <si>
-    <t>https://www.blackrock.com/es/profesionales/productos/337587</t>
-  </si>
-  <si>
     <t>ID30</t>
   </si>
   <si>
-    <t>https://www.blackrock.com/es/profesionales/productos/337573</t>
-  </si>
-  <si>
     <t>ID31</t>
   </si>
   <si>
@@ -144,6 +135,15 @@
   </si>
   <si>
     <t>https://www.ishares.com/uk/individual/en/products/291404/ishares-global-high-yield-corp-bond-ucits-etf</t>
+  </si>
+  <si>
+    <t>https://www.blackrock.com/es/profesionales/productos/331714/</t>
+  </si>
+  <si>
+    <t>https://www.blackrock.com/es/profesionales/productos/337587/</t>
+  </si>
+  <si>
+    <t>https://www.blackrock.com/es/profesionales/productos/337573/</t>
   </si>
 </sst>
 </file>
@@ -576,10 +576,10 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F2" s="4">
-        <v>4.7E-2</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>10</v>
+        <v>4.4699999999999997E-2</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -587,7 +587,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>9</v>
@@ -599,10 +599,10 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F3" s="4">
-        <v>4.8000000000000001E-2</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>12</v>
+        <v>4.6100000000000002E-2</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -610,7 +610,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
@@ -622,10 +622,10 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F4" s="4">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>14</v>
+        <v>4.7E-2</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -633,7 +633,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
@@ -645,10 +645,10 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F5" s="4">
-        <v>0.05</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>4.87E-2</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -656,7 +656,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>
@@ -668,10 +668,10 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F6" s="4">
-        <v>5.0999999999999997E-2</v>
+        <v>4.8899999999999999E-2</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -679,7 +679,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
@@ -691,10 +691,10 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F7" s="4">
-        <v>5.2499999999999998E-2</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>20</v>
+        <v>5.0700000000000002E-2</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -702,7 +702,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>9</v>
@@ -714,10 +714,10 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F8" s="4">
-        <v>5.3999999999999999E-2</v>
+        <v>5.21E-2</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -725,10 +725,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D9" s="2">
         <v>2028</v>
@@ -737,10 +737,10 @@
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="F9" s="4">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>25</v>
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -748,10 +748,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D10" s="2">
         <v>2029</v>
@@ -760,85 +760,95 @@
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="F10" s="4">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>27</v>
+        <v>6.8599999999999994E-2</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E11" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F11" s="4">
-        <v>6.7100000000000007E-2</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>31</v>
+        <v>7.0499999999999993E-2</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E12" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F12" s="4">
-        <v>6.8000000000000005E-2</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>33</v>
+        <v>6.4799999999999996E-2</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E13" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F13" s="4">
-        <v>6.4000000000000001E-2</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>35</v>
+        <v>6.1699999999999998E-2</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G6" r:id="rId1" xr:uid="{A136E316-D146-4C62-8997-940DB37BE250}"/>
-    <hyperlink ref="G8" r:id="rId2" xr:uid="{89B60FCD-B44A-4C7B-B904-5EA6C3E5C053}"/>
+    <hyperlink ref="G6" r:id="rId1" xr:uid="{B6117D84-CE17-4C39-97A4-2FECFBD9D72F}"/>
+    <hyperlink ref="G8" r:id="rId2" xr:uid="{C9B4AF5F-D445-4954-A5B4-9A9404647A98}"/>
+    <hyperlink ref="G2" r:id="rId3" xr:uid="{4F2398EC-A641-4AA0-B373-AACB76DC52AB}"/>
+    <hyperlink ref="G3" r:id="rId4" xr:uid="{4E26F537-5B70-4B16-AA9C-51E373C76E6B}"/>
+    <hyperlink ref="G4" r:id="rId5" xr:uid="{D68DB80B-5A3D-4437-89AC-3312CA0293CE}"/>
+    <hyperlink ref="G5" r:id="rId6" xr:uid="{C4AED9EB-79C7-4CA2-AB41-CBDCF6F62BB9}"/>
+    <hyperlink ref="G7" r:id="rId7" xr:uid="{15104A3C-DA04-45BC-B198-06F978BD9812}"/>
+    <hyperlink ref="G9" r:id="rId8" xr:uid="{9B90FFED-B168-4EA6-A362-72A119859FDE}"/>
+    <hyperlink ref="G10" r:id="rId9" xr:uid="{2CB0AA5D-72C2-4572-9F74-0D70D4C80223}"/>
+    <hyperlink ref="G11" r:id="rId10" xr:uid="{F511A075-C4D1-4CE9-A45D-7114C6233560}"/>
+    <hyperlink ref="G12" r:id="rId11" xr:uid="{02000FC9-624E-44CA-8C5A-15BA4F81D1E9}"/>
+    <hyperlink ref="G13" r:id="rId12" xr:uid="{2F14417C-9CE8-4828-96C7-488CC1D18402}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ETF.xlsx
+++ b/ETF.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Claude\Projects\Presentaciones de Quarter\Github Pagina\Bonos-FCA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2110CD71-1E1F-4EAA-A443-274577416446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F283BB-082B-44DA-BAA7-9DA9FF9C4D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -576,7 +576,7 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F2" s="4">
-        <v>4.4699999999999997E-2</v>
+        <v>4.7600000000000003E-2</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>33</v>
@@ -599,7 +599,7 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F3" s="4">
-        <v>4.6100000000000002E-2</v>
+        <v>4.9099999999999998E-2</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>34</v>
@@ -622,7 +622,7 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F4" s="4">
-        <v>4.7E-2</v>
+        <v>5.0099999999999999E-2</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>35</v>
@@ -645,7 +645,7 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F5" s="4">
-        <v>4.87E-2</v>
+        <v>5.1499999999999997E-2</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>13</v>
@@ -668,7 +668,7 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F6" s="4">
-        <v>4.8899999999999999E-2</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>15</v>
@@ -691,7 +691,7 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F7" s="4">
-        <v>5.0700000000000002E-2</v>
+        <v>5.3600000000000002E-2</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>17</v>
@@ -714,7 +714,7 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F8" s="4">
-        <v>5.21E-2</v>
+        <v>5.4899999999999997E-2</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>19</v>
@@ -737,7 +737,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="F9" s="4">
-        <v>6.5000000000000002E-2</v>
+        <v>6.83E-2</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>22</v>
@@ -760,7 +760,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="F10" s="4">
-        <v>6.8599999999999994E-2</v>
+        <v>7.2099999999999997E-2</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>24</v>
@@ -783,7 +783,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F11" s="4">
-        <v>7.0499999999999993E-2</v>
+        <v>6.7199999999999996E-2</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>28</v>
@@ -806,7 +806,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F12" s="4">
-        <v>6.4799999999999996E-2</v>
+        <v>6.8599999999999994E-2</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>30</v>
@@ -829,7 +829,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F13" s="4">
-        <v>6.1699999999999998E-2</v>
+        <v>6.5299999999999997E-2</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>32</v>

--- a/ETF.xlsx
+++ b/ETF.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Claude\Projects\Presentaciones de Quarter\Github Pagina\Bonos-FCA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F283BB-082B-44DA-BAA7-9DA9FF9C4D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479F5F14-CA81-4E23-8380-F6A0C15C8166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -576,7 +576,7 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F2" s="4">
-        <v>4.7600000000000003E-2</v>
+        <v>4.7500000000000001E-2</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>33</v>
@@ -599,7 +599,7 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F3" s="4">
-        <v>4.9099999999999998E-2</v>
+        <v>4.9399999999999999E-2</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>34</v>
@@ -622,7 +622,7 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F4" s="4">
-        <v>5.0099999999999999E-2</v>
+        <v>5.0900000000000001E-2</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>35</v>
@@ -645,7 +645,7 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F5" s="4">
-        <v>5.1499999999999997E-2</v>
+        <v>5.2499999999999998E-2</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>13</v>
@@ -668,7 +668,7 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F6" s="4">
-        <v>5.1999999999999998E-2</v>
+        <v>5.3100000000000001E-2</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>15</v>
@@ -691,7 +691,7 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F7" s="4">
-        <v>5.3600000000000002E-2</v>
+        <v>5.4800000000000001E-2</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>17</v>
@@ -714,7 +714,7 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="F8" s="4">
-        <v>5.4899999999999997E-2</v>
+        <v>5.5800000000000002E-2</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>19</v>
@@ -737,7 +737,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="F9" s="4">
-        <v>6.83E-2</v>
+        <v>6.8699999999999997E-2</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>22</v>
@@ -760,7 +760,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="F10" s="4">
-        <v>7.2099999999999997E-2</v>
+        <v>7.0800000000000002E-2</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>24</v>
@@ -783,7 +783,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F11" s="4">
-        <v>6.7199999999999996E-2</v>
+        <v>6.3200000000000006E-2</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>28</v>
@@ -806,7 +806,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F12" s="4">
-        <v>6.8599999999999994E-2</v>
+        <v>6.7299999999999999E-2</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>30</v>
@@ -829,7 +829,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F13" s="4">
-        <v>6.5299999999999997E-2</v>
+        <v>6.4799999999999996E-2</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>32</v>
